--- a/hardware/VoltTemp/VoltTempBOM.xlsx
+++ b/hardware/VoltTemp/VoltTempBOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lakshaygupta/Documents/LHR/BPS/BPS-VoltTempPCB/hardware/VoltTemp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1000d\Documents\LHR\BPS-VoltTemp\hardware\VoltTemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F13D03C6-FB9C-EE46-BEEE-E851B00954B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B1EF27-25BE-4CA6-9462-F81D578ABF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="740" windowWidth="28040" windowHeight="16680" xr2:uid="{EDF4FD0D-AE22-AE43-BC42-06DCD891D191}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EDF4FD0D-AE22-AE43-BC42-06DCD891D191}"/>
   </bookViews>
   <sheets>
     <sheet name="VoltTempBOM" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Reference</t>
   </si>
@@ -40,72 +40,6 @@
     <t>DNP</t>
   </si>
   <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>BQ_HB</t>
-  </si>
-  <si>
-    <t>XL-1608UBC-06A</t>
-  </si>
-  <si>
-    <t>LED_SMD:LED_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>3v3</t>
-  </si>
-  <si>
-    <t>R34,R38,R43,R44,R50</t>
-  </si>
-  <si>
-    <t>TNPU060327K0AYEN00</t>
-  </si>
-  <si>
-    <t>Resistor_SMD:R_0603_1608Metric_Pad0.98x0.95mm_HandSolder</t>
-  </si>
-  <si>
-    <t>U4,U6,U12,U13,U14</t>
-  </si>
-  <si>
-    <t>TLV9062xD</t>
-  </si>
-  <si>
-    <t>TLV9062QDGKRQ1</t>
-  </si>
-  <si>
-    <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>TL3365AF180QG</t>
-  </si>
-  <si>
-    <t>VoltTemp:SW_TL3365AF180QG</t>
-  </si>
-  <si>
-    <t>R25,R26,R28,R30</t>
-  </si>
-  <si>
-    <t>SFR03EZPJ000</t>
-  </si>
-  <si>
-    <t>R23,R24,R27</t>
-  </si>
-  <si>
-    <t>R35,R36,R39,R40,R45,R46,R47,R48,R51,R52</t>
-  </si>
-  <si>
-    <t>SFR03EZPF2701</t>
-  </si>
-  <si>
     <t>J5</t>
   </si>
   <si>
@@ -118,177 +52,6 @@
     <t>UTSVT_Connectors:CONN_SFH11-xxxC-D05-ST-XX_SUL</t>
   </si>
   <si>
-    <t>F7,F8,F9,F10,F11</t>
-  </si>
-  <si>
-    <t>10mA</t>
-  </si>
-  <si>
-    <t>PTSLR06038V075</t>
-  </si>
-  <si>
-    <t>VoltTemp:ptc_fuse_FUSC1607X75N</t>
-  </si>
-  <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>BQ-Fault</t>
-  </si>
-  <si>
-    <t>NCD0603R1</t>
-  </si>
-  <si>
-    <t>C3,C26,C28,C29,C32,C34,C35,C36,C37,C38,C39,C40,C41</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>MLASU168SB5105KTNA01</t>
-  </si>
-  <si>
-    <t>Capacitor_SMD:C_0603_1608Metric_Pad1.08x0.95mm_HandSolder,Capacitor_SMD:C_0805_2012Metric_Pad1.18x1.45mm_HandSolder</t>
-  </si>
-  <si>
-    <t>C10,C11,C12,C13,C14,C15,C16,C17</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>MLASH168SB7104KTNA01</t>
-  </si>
-  <si>
-    <t>Capacitor_SMD:C_0603_1608Metric_Pad1.08x0.95mm_HandSolder</t>
-  </si>
-  <si>
-    <t>C5,C6,C7,C8,C9,C24,C42</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>IC1</t>
-  </si>
-  <si>
-    <t>ISO1641BDR</t>
-  </si>
-  <si>
-    <t>VoltTemp:ISO1641BDR</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>GRM21BR61H106KE43K</t>
-  </si>
-  <si>
-    <t>Capacitor_SMD:C_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>40mA</t>
-  </si>
-  <si>
-    <t>FUSC1607X75N</t>
-  </si>
-  <si>
-    <t>R53,R54,R55,R56,R57,R58,R59,R60</t>
-  </si>
-  <si>
-    <t>100Œ©</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESR03EZPF1000 </t>
-  </si>
-  <si>
-    <t>R1,R37,R41,R42,R49</t>
-  </si>
-  <si>
-    <t>8.2kŒ©</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERA-3AED822V </t>
-  </si>
-  <si>
-    <t>U1,U3</t>
-  </si>
-  <si>
-    <t>EL3H7</t>
-  </si>
-  <si>
-    <t>EL3H7(D)(TA)-VG</t>
-  </si>
-  <si>
-    <t>UTSVT_ICs:EL3H7</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
-    <t>4.3k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCW06034K30FKTA </t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCW06032K10FKEA </t>
-  </si>
-  <si>
-    <t>Resistor_SMD:R_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>R8,R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCW06031K00FKEI </t>
-  </si>
-  <si>
-    <t>R9,R10,R11,R13,R14,R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCW060310K0FKEI </t>
-  </si>
-  <si>
-    <t>R18,R19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCW0603120RFKEC </t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>CPF0603B510KE1</t>
-  </si>
-  <si>
-    <t>C25,C27,C30,C31,C33</t>
-  </si>
-  <si>
-    <t>1.2uF</t>
-  </si>
-  <si>
-    <t>C0805C125K4RACTU</t>
-  </si>
-  <si>
-    <t>Capacitor_SMD:C_0805_2012Metric_Pad1.18x1.45mm_HandSolder</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>BQ7692003PW</t>
-  </si>
-  <si>
-    <t>VoltTemp:BQ7692003PW</t>
-  </si>
-  <si>
     <t>J10</t>
   </si>
   <si>
@@ -298,36 +61,6 @@
     <t>UTSVT_Connectors:PeripheralSOM</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D_Zener_Small</t>
-  </si>
-  <si>
-    <t>1N448W</t>
-  </si>
-  <si>
-    <t>Diode_SMD:D_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>08055D475KAT4A</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>470pF</t>
-  </si>
-  <si>
-    <t>06035C471J4Z2A</t>
-  </si>
-  <si>
     <t>J6,J7,J12,J13</t>
   </si>
   <si>
@@ -362,36 +95,6 @@
   </si>
   <si>
     <t>VoltTemp:1053131103</t>
-  </si>
-  <si>
-    <t>D2,D3,D4,D5,D6,D7,D8,D9</t>
-  </si>
-  <si>
-    <t>WS2812B-2020</t>
-  </si>
-  <si>
-    <t>LED_SMD:LED_WS2812B-2020_PLCC4_2.0x2.0mm</t>
-  </si>
-  <si>
-    <t>2k</t>
-  </si>
-  <si>
-    <t>1k</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>510k</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>2.7k</t>
-  </si>
-  <si>
-    <t>27k</t>
   </si>
 </sst>
 </file>
@@ -1252,13 +955,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040EEF98-97D1-4547-8097-5D942ECC92BF}">
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1295,7 +998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1303,605 +1006,81 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>1053132104</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
         <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1053131107</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6">
+        <v>1053131106</v>
+      </c>
+      <c r="D6" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C7">
+        <v>1053131103</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
       <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10">
         <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26">
-        <v>120</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34">
-        <v>1053132104</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35">
-        <v>1053131107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36">
-        <v>1053131106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>111</v>
-      </c>
-      <c r="B37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37">
-        <v>1053131103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
